--- a/latin/id_list.xlsx
+++ b/latin/id_list.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="698">
   <si>
     <t>id_aconitus</t>
   </si>
@@ -2056,6 +2056,60 @@
   </si>
   <si>
     <t>id_advento</t>
+  </si>
+  <si>
+    <t>id_bos</t>
+  </si>
+  <si>
+    <t>Bōs, bovis</t>
+  </si>
+  <si>
+    <t>Ager, agrī</t>
+  </si>
+  <si>
+    <t>Vitulus, -ī</t>
+  </si>
+  <si>
+    <t>Terĕs, teretis</t>
+  </si>
+  <si>
+    <t>Referō, refers, rettulī, relātum, referre</t>
+  </si>
+  <si>
+    <t>Armentum, -ī</t>
+  </si>
+  <si>
+    <t>Permaneō, permanēs, permānsī, permānsum, permanēre</t>
+  </si>
+  <si>
+    <t>Pŏstmŏdum, pŏstmŏdŏ</t>
+  </si>
+  <si>
+    <t>Crūs, crūris</t>
+  </si>
+  <si>
+    <t>Tegō, tegis, tēxī, tēctum, tegĕre</t>
+  </si>
+  <si>
+    <t>Velut / velutī</t>
+  </si>
+  <si>
+    <t>conj.</t>
+  </si>
+  <si>
+    <t>Adūrō, adūris, adussī, adŭstum, adūrĕre</t>
+  </si>
+  <si>
+    <t>Tamdiū</t>
+  </si>
+  <si>
+    <t>Sūgō, sūgis, sūxī, sūctum, sūgĕre</t>
+  </si>
+  <si>
+    <t>Quoad</t>
+  </si>
+  <si>
+    <t>Convertō, convertis, convertī, conversum, convertĕre</t>
   </si>
 </sst>
 </file>
@@ -2397,7 +2451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E509"/>
+  <dimension ref="A1:E510"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.140625" style="1" customWidth="1"/>
@@ -2569,6 +2623,12 @@
       <c r="B17" s="1" t="s">
         <v>113</v>
       </c>
+      <c r="C17" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
@@ -2590,6 +2650,12 @@
       </c>
       <c r="B19" s="1" t="s">
         <v>114</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2835,6 +2901,12 @@
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
+      <c r="C42" t="s">
+        <v>686</v>
+      </c>
+      <c r="D42" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
@@ -2970,17 +3042,17 @@
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="1" t="s">
-        <v>453</v>
+      <c r="A57" s="2" t="s">
+        <v>614</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>9</v>
+        <v>680</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>462</v>
+        <v>681</v>
+      </c>
+      <c r="D57" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2988,10 +3060,13 @@
         <v>453</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2999,35 +3074,32 @@
         <v>453</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>138</v>
+        <v>11</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>514</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3035,18 +3107,24 @@
         <v>453</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>479</v>
+        <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>478</v>
+        <v>458</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>13</v>
+        <v>479</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3054,29 +3132,29 @@
         <v>614</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>462</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>140</v>
+        <v>14</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3084,21 +3162,15 @@
         <v>614</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>527</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3106,18 +3178,24 @@
         <v>453</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>15</v>
+        <v>525</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>481</v>
+        <v>526</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>142</v>
+        <v>15</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3125,7 +3203,7 @@
         <v>614</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3133,7 +3211,7 @@
         <v>614</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3141,48 +3219,48 @@
         <v>614</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="s">
-        <v>611</v>
-      </c>
-      <c r="D74" t="s">
-        <v>544</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>146</v>
+        <v>16</v>
+      </c>
+      <c r="C75" t="s">
+        <v>611</v>
+      </c>
+      <c r="D75" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>482</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>147</v>
+        <v>17</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3190,13 +3268,7 @@
         <v>614</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>470</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3204,7 +3276,13 @@
         <v>614</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3212,7 +3290,7 @@
         <v>614</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3220,7 +3298,7 @@
         <v>614</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3228,7 +3306,7 @@
         <v>614</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3236,7 +3314,7 @@
         <v>614</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3244,7 +3322,7 @@
         <v>614</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3252,29 +3330,29 @@
         <v>614</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>544</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>156</v>
+        <v>18</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3282,7 +3360,7 @@
         <v>614</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3290,7 +3368,7 @@
         <v>614</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3298,7 +3376,7 @@
         <v>614</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3306,7 +3384,7 @@
         <v>614</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3314,7 +3392,7 @@
         <v>614</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3322,7 +3400,7 @@
         <v>614</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3330,7 +3408,7 @@
         <v>614</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3338,7 +3416,7 @@
         <v>614</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3346,7 +3424,7 @@
         <v>614</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3354,7 +3432,7 @@
         <v>614</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3362,7 +3440,7 @@
         <v>614</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3370,7 +3448,7 @@
         <v>614</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3378,7 +3456,7 @@
         <v>614</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3386,7 +3464,7 @@
         <v>614</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3394,7 +3472,7 @@
         <v>614</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3402,51 +3480,51 @@
         <v>614</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B104" t="s">
-        <v>613</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>545</v>
+        <v>614</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>19</v>
+      <c r="B105" t="s">
+        <v>613</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>483</v>
+        <v>612</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="C106" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>173</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3454,43 +3532,43 @@
         <v>614</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>473</v>
+        <v>174</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C110" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>473</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3498,40 +3576,46 @@
         <v>453</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>175</v>
+        <v>22</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>489</v>
+        <v>175</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>176</v>
+        <v>441</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3539,7 +3623,7 @@
         <v>614</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3547,7 +3631,7 @@
         <v>614</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3555,7 +3639,7 @@
         <v>614</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3563,13 +3647,13 @@
         <v>614</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>669</v>
+        <v>179</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3577,32 +3661,32 @@
         <v>614</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>180</v>
+        <v>669</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>544</v>
+        <v>180</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>637</v>
+        <v>490</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>544</v>
@@ -3613,7 +3697,13 @@
         <v>614</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3621,7 +3711,7 @@
         <v>614</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3637,7 +3727,7 @@
         <v>614</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3645,7 +3735,7 @@
         <v>614</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3653,7 +3743,7 @@
         <v>614</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -3661,10 +3751,7 @@
         <v>614</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C129" t="s">
-        <v>514</v>
+        <v>186</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -3672,7 +3759,10 @@
         <v>614</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
+      </c>
+      <c r="C130" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3680,7 +3770,7 @@
         <v>614</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -3688,26 +3778,26 @@
         <v>614</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>557</v>
+        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>191</v>
+        <v>24</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -3715,7 +3805,7 @@
         <v>614</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -3723,7 +3813,7 @@
         <v>614</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -3731,7 +3821,7 @@
         <v>614</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -3739,26 +3829,26 @@
         <v>614</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>492</v>
+        <v>195</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>196</v>
+        <v>491</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -3766,7 +3856,7 @@
         <v>614</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -3774,7 +3864,7 @@
         <v>614</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -3782,7 +3872,7 @@
         <v>614</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -3790,21 +3880,15 @@
         <v>614</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>531</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3812,46 +3896,52 @@
         <v>453</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>25</v>
+        <v>449</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>465</v>
+        <v>531</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>201</v>
+        <v>25</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>673</v>
+        <v>515</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>544</v>
+        <v>465</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>450</v>
+        <v>201</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>536</v>
+        <v>673</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>202</v>
+        <v>450</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3859,40 +3949,37 @@
         <v>614</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>465</v>
+        <v>203</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>204</v>
+        <v>26</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="B153" t="s">
-        <v>665</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>664</v>
+      <c r="B153" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3900,24 +3987,24 @@
         <v>614</v>
       </c>
       <c r="B154" t="s">
-        <v>205</v>
+        <v>665</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="D154" t="s">
-        <v>546</v>
+        <v>664</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>514</v>
+      <c r="B155" t="s">
+        <v>205</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="D155" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3925,7 +4012,10 @@
         <v>614</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3933,7 +4023,7 @@
         <v>614</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3941,7 +4031,7 @@
         <v>614</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3949,7 +4039,7 @@
         <v>614</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3957,7 +4047,7 @@
         <v>614</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3965,62 +4055,56 @@
         <v>614</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>561</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="C163" s="1" t="s">
+        <v>561</v>
+      </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>213</v>
+        <v>27</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>473</v>
+        <v>213</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>214</v>
+        <v>616</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>650</v>
+        <v>615</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>546</v>
+        <v>473</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4028,7 +4112,13 @@
         <v>614</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4036,7 +4126,7 @@
         <v>614</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4044,24 +4134,24 @@
         <v>614</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C169" s="2"/>
+        <v>216</v>
+      </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>218</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="C170" s="2"/>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4069,7 +4159,7 @@
         <v>614</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4077,7 +4167,7 @@
         <v>614</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4085,7 +4175,7 @@
         <v>614</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4093,7 +4183,7 @@
         <v>614</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4101,7 +4191,7 @@
         <v>614</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4109,7 +4199,7 @@
         <v>614</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4117,7 +4207,7 @@
         <v>614</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4125,21 +4215,15 @@
         <v>614</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>618</v>
+        <v>227</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4147,35 +4231,35 @@
         <v>453</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>563</v>
+        <v>617</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>465</v>
+        <v>618</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>228</v>
+        <v>564</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C183" t="s">
-        <v>621</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>465</v>
+        <v>228</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4183,48 +4267,54 @@
         <v>453</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>511</v>
+        <v>29</v>
+      </c>
+      <c r="C184" t="s">
+        <v>621</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B185" t="s">
+        <v>453</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>547</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>622</v>
+        <v>614</v>
+      </c>
+      <c r="B186" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B187" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>229</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
-      <c r="A188" t="s">
-        <v>614</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4232,15 +4322,15 @@
         <v>614</v>
       </c>
       <c r="B189" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
+        <v>614</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>675</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
-      <c r="A190" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4248,29 +4338,29 @@
         <v>614</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>465</v>
+        <v>232</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>233</v>
+        <v>31</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4278,51 +4368,51 @@
         <v>614</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C195" t="s">
-        <v>623</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>473</v>
+        <v>234</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>235</v>
+        <v>32</v>
+      </c>
+      <c r="C196" t="s">
+        <v>623</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>462</v>
+        <v>235</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>236</v>
+        <v>33</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4330,13 +4420,7 @@
         <v>614</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="D199" t="s">
-        <v>668</v>
+        <v>236</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4344,43 +4428,43 @@
         <v>614</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>237</v>
+        <v>666</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="D200" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>465</v>
+        <v>237</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>238</v>
+        <v>34</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>462</v>
+        <v>238</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4388,13 +4472,13 @@
         <v>453</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>509</v>
+        <v>35</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>508</v>
+        <v>619</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>544</v>
+        <v>462</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4402,18 +4486,24 @@
         <v>453</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>36</v>
+        <v>509</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>560</v>
+        <v>508</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>239</v>
+        <v>36</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4421,21 +4511,15 @@
         <v>614</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>462</v>
+        <v>240</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4443,70 +4527,73 @@
         <v>453</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>620</v>
+        <v>566</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>544</v>
+        <v>462</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="C210" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>241</v>
+        <v>38</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>242</v>
+        <v>39</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="B214" t="s">
-        <v>674</v>
+      <c r="B214" s="1" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>568</v>
+        <v>614</v>
+      </c>
+      <c r="B215" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4514,21 +4601,24 @@
         <v>453</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>545</v>
+        <v>568</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>243</v>
+        <v>41</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4536,43 +4626,37 @@
         <v>614</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>462</v>
+        <v>244</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>245</v>
+        <v>42</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>488</v>
+        <v>245</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4580,43 +4664,49 @@
         <v>453</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C222" t="s">
-        <v>656</v>
-      </c>
-      <c r="D222" t="s">
-        <v>586</v>
+        <v>443</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>246</v>
+        <v>655</v>
+      </c>
+      <c r="C223" t="s">
+        <v>656</v>
+      </c>
+      <c r="D223" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>545</v>
+        <v>246</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>247</v>
+        <v>43</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4624,7 +4714,7 @@
         <v>614</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4632,70 +4722,70 @@
         <v>614</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>462</v>
+        <v>249</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B229" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
-      <c r="A230" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B230" t="s">
+    <row r="231" spans="1:4">
+      <c r="A231" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B231" t="s">
         <v>643</v>
       </c>
-      <c r="C230" s="1" t="s">
+      <c r="C231" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D231" t="s">
         <v>544</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4">
-      <c r="A231" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>624</v>
+        <v>251</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>252</v>
+        <v>452</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4703,7 +4793,7 @@
         <v>614</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4711,7 +4801,7 @@
         <v>614</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4719,7 +4809,7 @@
         <v>614</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4727,26 +4817,26 @@
         <v>614</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>573</v>
+        <v>256</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>257</v>
+        <v>45</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4754,7 +4844,7 @@
         <v>614</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4762,7 +4852,7 @@
         <v>614</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4770,7 +4860,7 @@
         <v>614</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4778,7 +4868,7 @@
         <v>614</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4786,7 +4876,7 @@
         <v>614</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4794,7 +4884,7 @@
         <v>614</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4802,7 +4892,7 @@
         <v>614</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4810,29 +4900,29 @@
         <v>614</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>578</v>
+        <v>265</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>266</v>
+        <v>46</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4840,29 +4930,29 @@
         <v>614</v>
       </c>
       <c r="B250" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
-      <c r="A251" t="s">
-        <v>453</v>
-      </c>
-      <c r="B251" s="1" t="s">
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
+        <v>453</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C251" s="1" t="s">
+      <c r="C252" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D251" s="1" t="s">
+      <c r="D252" s="1" t="s">
         <v>518</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
-      <c r="A252" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4870,29 +4960,29 @@
         <v>614</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>543</v>
+        <v>269</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>270</v>
+        <v>448</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4900,7 +4990,7 @@
         <v>614</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4908,7 +4998,7 @@
         <v>614</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4916,21 +5006,15 @@
         <v>614</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="C259" t="s">
-        <v>633</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>455</v>
+        <v>273</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4938,57 +5022,57 @@
         <v>453</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>502</v>
+        <v>542</v>
+      </c>
+      <c r="C260" t="s">
+        <v>633</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>544</v>
+        <v>455</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>274</v>
+        <v>503</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>465</v>
+        <v>274</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>275</v>
+        <v>47</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>465</v>
+        <v>275</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4996,21 +5080,27 @@
         <v>453</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C265" t="s">
-        <v>631</v>
+        <v>48</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>544</v>
+        <v>465</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>276</v>
+        <v>49</v>
+      </c>
+      <c r="C266" t="s">
+        <v>631</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5018,7 +5108,7 @@
         <v>614</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5026,29 +5116,29 @@
         <v>614</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="C269" t="s">
-        <v>635</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>465</v>
+        <v>278</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>279</v>
+        <v>634</v>
+      </c>
+      <c r="C270" t="s">
+        <v>635</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5056,7 +5146,7 @@
         <v>614</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5064,21 +5154,15 @@
         <v>614</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>577</v>
+        <v>281</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5086,18 +5170,24 @@
         <v>453</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>538</v>
+        <v>576</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>282</v>
+        <v>51</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5105,7 +5195,7 @@
         <v>614</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5113,7 +5203,7 @@
         <v>614</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5121,21 +5211,15 @@
         <v>614</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C279" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>455</v>
+        <v>285</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5143,21 +5227,27 @@
         <v>453</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>451</v>
+        <v>52</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>286</v>
+        <v>451</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5165,7 +5255,7 @@
         <v>614</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5173,7 +5263,7 @@
         <v>614</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5181,59 +5271,59 @@
         <v>614</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>583</v>
+        <v>289</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>290</v>
+        <v>53</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C287" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>578</v>
+        <v>290</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>291</v>
       </c>
+      <c r="C288" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5241,51 +5331,51 @@
         <v>614</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C291" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>462</v>
+        <v>293</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>294</v>
+        <v>54</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>545</v>
+        <v>294</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>295</v>
+        <v>55</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5293,139 +5383,139 @@
         <v>614</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>465</v>
+        <v>296</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>297</v>
+        <v>447</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>462</v>
+        <v>297</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>298</v>
+        <v>56</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C300" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>506</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>299</v>
+        <v>507</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>586</v>
+        <v>299</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="C303" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C304" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>544</v>
+        <v>57</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>300</v>
+        <v>58</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>462</v>
+        <v>300</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>301</v>
+        <v>59</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5433,7 +5523,7 @@
         <v>614</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5441,7 +5531,7 @@
         <v>614</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5449,7 +5539,7 @@
         <v>614</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5457,29 +5547,29 @@
         <v>614</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>544</v>
+        <v>305</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>306</v>
+        <v>60</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5487,7 +5577,7 @@
         <v>614</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5495,7 +5585,7 @@
         <v>614</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5503,51 +5593,51 @@
         <v>614</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>462</v>
+        <v>309</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>310</v>
+        <v>493</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>473</v>
+        <v>310</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>311</v>
+        <v>61</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5555,7 +5645,7 @@
         <v>614</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5563,7 +5653,7 @@
         <v>614</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5571,48 +5661,48 @@
         <v>614</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>629</v>
+        <v>314</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>315</v>
+        <v>62</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>546</v>
+        <v>315</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>316</v>
+        <v>63</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5620,26 +5710,26 @@
         <v>614</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>627</v>
+        <v>317</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>318</v>
+        <v>64</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5647,7 +5737,7 @@
         <v>614</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5655,29 +5745,29 @@
         <v>614</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>577</v>
+        <v>320</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>321</v>
+        <v>65</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5685,7 +5775,7 @@
         <v>614</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5693,7 +5783,7 @@
         <v>614</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5701,7 +5791,7 @@
         <v>614</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5709,7 +5799,13 @@
         <v>614</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5717,7 +5813,7 @@
         <v>614</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5725,29 +5821,29 @@
         <v>614</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>462</v>
+        <v>327</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>328</v>
+        <v>66</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5755,7 +5851,7 @@
         <v>614</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5763,7 +5859,7 @@
         <v>614</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5771,29 +5867,29 @@
         <v>614</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>462</v>
+        <v>331</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>67</v>
+        <v>332</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5801,7 +5897,7 @@
         <v>614</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>333</v>
+        <v>67</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5809,26 +5905,26 @@
         <v>614</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>335</v>
+        <v>68</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5836,29 +5932,35 @@
         <v>614</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>593</v>
+        <v>336</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>337</v>
+        <v>69</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5866,13 +5968,7 @@
         <v>614</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>543</v>
+        <v>337</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5880,7 +5976,13 @@
         <v>614</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>338</v>
+        <v>653</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5888,29 +5990,29 @@
         <v>614</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>544</v>
+        <v>339</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>340</v>
+        <v>70</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5918,7 +6020,7 @@
         <v>614</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5926,7 +6028,7 @@
         <v>614</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5934,26 +6036,26 @@
         <v>614</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C363" s="1" t="s">
-        <v>541</v>
+        <v>343</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>344</v>
+        <v>540</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5961,7 +6063,7 @@
         <v>614</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5969,21 +6071,15 @@
         <v>614</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C367" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>462</v>
+        <v>346</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5991,26 +6087,32 @@
         <v>453</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="C369" s="1" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>347</v>
+        <v>72</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6018,7 +6120,7 @@
         <v>614</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6026,13 +6128,7 @@
         <v>614</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C372" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="D372" s="1" t="s">
-        <v>544</v>
+        <v>348</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6040,27 +6136,33 @@
         <v>614</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D373" s="2"/>
+        <v>676</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="374" spans="1:4">
       <c r="A374" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>500</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="D374" s="2"/>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>350</v>
+        <v>501</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6068,7 +6170,7 @@
         <v>614</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6076,7 +6178,7 @@
         <v>614</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6084,13 +6186,7 @@
         <v>614</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>618</v>
+        <v>352</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6098,7 +6194,13 @@
         <v>614</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>353</v>
+        <v>662</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6106,7 +6208,7 @@
         <v>614</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6114,7 +6216,7 @@
         <v>614</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6122,7 +6224,7 @@
         <v>614</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6130,7 +6232,7 @@
         <v>614</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6138,43 +6240,43 @@
         <v>614</v>
       </c>
       <c r="B384" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B385" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="385" spans="1:4">
-      <c r="A385" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="B385" t="s">
+      <c r="C385" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B386" t="s">
         <v>647</v>
       </c>
-      <c r="C385" s="1" t="s">
+      <c r="C386" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="D385" t="s">
+      <c r="D386" t="s">
         <v>470</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4">
-      <c r="A386" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B386" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C387" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="D387" s="1" t="s">
-        <v>465</v>
+        <v>359</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6182,29 +6284,35 @@
         <v>453</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>73</v>
+        <v>442</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="C389" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>360</v>
+        <v>73</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6212,29 +6320,29 @@
         <v>614</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="D392" s="1" t="s">
-        <v>544</v>
+        <v>361</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>362</v>
+        <v>74</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6242,7 +6350,7 @@
         <v>614</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6250,7 +6358,7 @@
         <v>614</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6258,29 +6366,35 @@
         <v>614</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C397" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D397" s="1" t="s">
-        <v>544</v>
+        <v>365</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>366</v>
+        <v>75</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6288,7 +6402,7 @@
         <v>614</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6296,7 +6410,7 @@
         <v>614</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6304,7 +6418,7 @@
         <v>614</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6312,7 +6426,7 @@
         <v>614</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6320,7 +6434,7 @@
         <v>614</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6328,7 +6442,7 @@
         <v>614</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6336,7 +6450,7 @@
         <v>614</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6344,7 +6458,7 @@
         <v>614</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6352,29 +6466,29 @@
         <v>614</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="D408" t="s">
-        <v>607</v>
+        <v>375</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>376</v>
+        <v>76</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D409" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6382,21 +6496,15 @@
         <v>614</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C411" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="D411" s="1" t="s">
-        <v>577</v>
+        <v>377</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6404,57 +6512,57 @@
         <v>453</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C412" t="s">
-        <v>651</v>
-      </c>
-      <c r="D412" t="s">
-        <v>578</v>
+        <v>77</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>378</v>
+        <v>652</v>
+      </c>
+      <c r="C413" t="s">
+        <v>651</v>
+      </c>
+      <c r="D413" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="D414" s="1" t="s">
-        <v>609</v>
+        <v>378</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="C415" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>609</v>
+      </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C416" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="D416" s="1" t="s">
-        <v>465</v>
+        <v>78</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6462,43 +6570,49 @@
         <v>453</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>604</v>
+        <v>556</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>577</v>
+        <v>465</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="C418" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>577</v>
+      </c>
     </row>
     <row r="419" spans="1:4">
       <c r="A419" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C419" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D419" s="1" t="s">
-        <v>543</v>
+        <v>80</v>
       </c>
     </row>
     <row r="420" spans="1:4">
       <c r="A420" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>379</v>
+        <v>81</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6506,7 +6620,7 @@
         <v>614</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6514,7 +6628,7 @@
         <v>614</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6522,7 +6636,7 @@
         <v>614</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6530,7 +6644,7 @@
         <v>614</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6538,7 +6652,7 @@
         <v>614</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6546,21 +6660,15 @@
         <v>614</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="427" spans="1:4">
       <c r="A427" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="D427" s="1" t="s">
-        <v>577</v>
+        <v>385</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6568,21 +6676,27 @@
         <v>453</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>532</v>
+        <v>603</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>462</v>
+        <v>577</v>
       </c>
     </row>
     <row r="429" spans="1:4">
       <c r="A429" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>386</v>
+        <v>83</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6590,7 +6704,7 @@
         <v>614</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6598,7 +6712,7 @@
         <v>614</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6606,51 +6720,51 @@
         <v>614</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="433" spans="1:4">
       <c r="A433" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C433" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="D433" s="1" t="s">
-        <v>544</v>
+        <v>389</v>
       </c>
     </row>
     <row r="434" spans="1:4">
       <c r="A434" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>390</v>
       </c>
+      <c r="C434" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="435" spans="1:4">
       <c r="A435" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C435" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="D435" s="1" t="s">
-        <v>577</v>
+        <v>390</v>
       </c>
     </row>
     <row r="436" spans="1:4">
       <c r="A436" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>391</v>
+        <v>84</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6658,26 +6772,26 @@
         <v>614</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="438" spans="1:4">
       <c r="A438" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>528</v>
+        <v>392</v>
       </c>
     </row>
     <row r="439" spans="1:4">
       <c r="A439" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>393</v>
+        <v>85</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6685,13 +6799,7 @@
         <v>614</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="D440" t="s">
-        <v>470</v>
+        <v>393</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6699,7 +6807,13 @@
         <v>614</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>394</v>
+        <v>645</v>
+      </c>
+      <c r="C441" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D441" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6707,7 +6821,7 @@
         <v>614</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6715,7 +6829,7 @@
         <v>614</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6723,7 +6837,7 @@
         <v>614</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6731,7 +6845,7 @@
         <v>614</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6739,43 +6853,40 @@
         <v>614</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="447" spans="1:4">
       <c r="A447" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C447" t="s">
-        <v>602</v>
-      </c>
-      <c r="D447" t="s">
-        <v>543</v>
+        <v>399</v>
       </c>
     </row>
     <row r="448" spans="1:4">
       <c r="A448" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B448" t="s">
-        <v>601</v>
-      </c>
-      <c r="C448" s="1" t="s">
-        <v>522</v>
+      <c r="B448" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C448" t="s">
+        <v>602</v>
+      </c>
+      <c r="D448" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="449" spans="1:4">
       <c r="A449" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B449" s="1" t="s">
-        <v>534</v>
+      <c r="B449" t="s">
+        <v>601</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6783,29 +6894,32 @@
         <v>453</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>87</v>
+        <v>534</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="D450" s="1" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
     </row>
     <row r="451" spans="1:4">
       <c r="A451" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="C451" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D451" s="1" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="452" spans="1:4">
       <c r="A452" s="1" t="s">
         <v>614</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6813,7 +6927,7 @@
         <v>614</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6821,7 +6935,7 @@
         <v>614</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6829,51 +6943,57 @@
         <v>614</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="456" spans="1:4">
       <c r="A456" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C456" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="D456" s="1" t="s">
-        <v>544</v>
+        <v>403</v>
       </c>
     </row>
     <row r="457" spans="1:4">
       <c r="A457" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>404</v>
+        <v>88</v>
+      </c>
+      <c r="C457" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D457" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="458" spans="1:4">
       <c r="A458" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>89</v>
+        <v>404</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>554</v>
+        <v>695</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
     </row>
     <row r="459" spans="1:4">
       <c r="A459" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>405</v>
+        <v>89</v>
+      </c>
+      <c r="C459" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D459" s="1" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -6881,7 +7001,7 @@
         <v>614</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6889,7 +7009,7 @@
         <v>614</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6897,7 +7017,7 @@
         <v>614</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -6905,7 +7025,13 @@
         <v>614</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
+      </c>
+      <c r="C463" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="D463" s="1" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -6913,29 +7039,35 @@
         <v>614</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="465" spans="1:5">
       <c r="A465" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>90</v>
+        <v>410</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>553</v>
+        <v>690</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>462</v>
+        <v>544</v>
       </c>
     </row>
     <row r="466" spans="1:5">
       <c r="A466" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>411</v>
+        <v>90</v>
+      </c>
+      <c r="C466" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D466" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -6943,7 +7075,7 @@
         <v>614</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -6951,29 +7083,29 @@
         <v>614</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="469" spans="1:5">
       <c r="A469" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C469" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="D469" s="1" t="s">
-        <v>546</v>
+        <v>413</v>
       </c>
     </row>
     <row r="470" spans="1:5">
       <c r="A470" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>414</v>
+        <v>91</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D470" s="1" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -6981,7 +7113,13 @@
         <v>614</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D471" s="1" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -6989,13 +7127,7 @@
         <v>614</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="D472" s="1" t="s">
-        <v>544</v>
+        <v>415</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -7003,7 +7135,13 @@
         <v>614</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D473" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -7011,7 +7149,7 @@
         <v>614</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -7019,7 +7157,7 @@
         <v>614</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -7027,13 +7165,7 @@
         <v>614</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="C476" t="s">
-        <v>649</v>
-      </c>
-      <c r="D476" t="s">
-        <v>577</v>
+        <v>419</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -7041,18 +7173,21 @@
         <v>614</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>420</v>
+        <v>648</v>
+      </c>
+      <c r="C477" t="s">
+        <v>649</v>
+      </c>
+      <c r="D477" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="478" spans="1:5">
       <c r="A478" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C478" s="1" t="s">
-        <v>537</v>
+        <v>420</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -7060,21 +7195,24 @@
         <v>453</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="E479" s="1" t="s">
-        <v>514</v>
+        <v>537</v>
       </c>
     </row>
     <row r="480" spans="1:5">
       <c r="A480" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>421</v>
+        <v>93</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E480" s="1" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7082,7 +7220,7 @@
         <v>614</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -7090,7 +7228,7 @@
         <v>614</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7098,7 +7236,7 @@
         <v>614</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -7106,29 +7244,29 @@
         <v>614</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="485" spans="1:4">
       <c r="A485" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C485" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="D485" s="1" t="s">
-        <v>544</v>
+        <v>425</v>
       </c>
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>426</v>
+        <v>94</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="D486" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -7136,7 +7274,7 @@
         <v>614</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7144,7 +7282,7 @@
         <v>614</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -7152,7 +7290,7 @@
         <v>614</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -7160,7 +7298,7 @@
         <v>614</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -7168,89 +7306,95 @@
         <v>614</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="C492" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="D492" s="1" t="s">
-        <v>473</v>
+        <v>431</v>
       </c>
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>432</v>
+        <v>446</v>
+      </c>
+      <c r="C493" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D493" s="1" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>504</v>
+        <v>691</v>
+      </c>
+      <c r="D494" s="1" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>433</v>
+        <v>445</v>
+      </c>
+      <c r="C495" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="D496" s="1" t="s">
-        <v>473</v>
+        <v>433</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>434</v>
+        <v>444</v>
+      </c>
+      <c r="C497" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D497" s="1" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C498" s="1" t="s">
-        <v>504</v>
+        <v>434</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>435</v>
+        <v>510</v>
+      </c>
+      <c r="C499" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7258,7 +7402,7 @@
         <v>614</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -7266,7 +7410,7 @@
         <v>614</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -7274,35 +7418,29 @@
         <v>614</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B503" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="D503" s="1" t="s">
-        <v>546</v>
+        <v>614</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B504" s="1" t="s">
-        <v>96</v>
+      <c r="B504" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>549</v>
+        <v>632</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>488</v>
+        <v>546</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7310,21 +7448,27 @@
         <v>453</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>544</v>
+        <v>488</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>439</v>
+        <v>97</v>
+      </c>
+      <c r="C506" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D506" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7332,34 +7476,48 @@
         <v>614</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D507" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C508" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="D508" s="1" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1" t="s">
-        <v>614</v>
+        <v>453</v>
       </c>
       <c r="B509" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D509" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B510" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C509" s="1" t="s">
+      <c r="C510" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="D509" s="1" t="s">
+      <c r="D510" s="1" t="s">
         <v>465</v>
       </c>
     </row>
